--- a/diseases/d109/1995-1999.xlsx
+++ b/diseases/d109/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>26</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>17</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>24</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>9</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>21</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>19</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>15</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>22</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>28</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>9</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>44</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>14</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>44</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>13</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>45</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>23</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>41</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>13</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>16</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>13</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>28</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>18</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>30</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>15</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>28</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>46</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>3</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>28</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>7</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>46</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>7</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>63</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>11</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>58</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>21</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>49</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>19</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>38</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>21</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>21</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>7</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>23</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20249,9 +20102,6 @@
       <c r="O101" t="n">
         <v>14</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20642,9 +20492,6 @@
       <c r="O103" t="n">
         <v>18</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21262,9 +21109,6 @@
       <c r="O106" t="n">
         <v>4</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21655,9 +21499,6 @@
       <c r="O108" t="n">
         <v>22</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22275,9 +22116,6 @@
       <c r="O111" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22668,9 +22506,6 @@
       <c r="O113" t="n">
         <v>17</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23288,9 +23123,6 @@
       <c r="O116" t="n">
         <v>4</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23681,9 +23513,6 @@
       <c r="O118" t="n">
         <v>21</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24301,9 +24130,6 @@
       <c r="O121" t="n">
         <v>9</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24694,9 +24520,6 @@
       <c r="O123" t="n">
         <v>32</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25314,9 +25137,6 @@
       <c r="O126" t="n">
         <v>6</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25707,9 +25527,6 @@
       <c r="O128" t="n">
         <v>49</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26327,9 +26144,6 @@
       <c r="O131" t="n">
         <v>8</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26720,9 +26534,6 @@
       <c r="O133" t="n">
         <v>93</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27340,9 +27151,6 @@
       <c r="O136" t="n">
         <v>16</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27733,9 +27541,6 @@
       <c r="O138" t="n">
         <v>103</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28353,9 +28158,6 @@
       <c r="O141" t="n">
         <v>25</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28746,9 +28548,6 @@
       <c r="O143" t="n">
         <v>78</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29366,9 +29165,6 @@
       <c r="O146" t="n">
         <v>25</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29759,9 +29555,6 @@
       <c r="O148" t="n">
         <v>48</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30379,9 +30172,6 @@
       <c r="O151" t="n">
         <v>14</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30772,9 +30562,6 @@
       <c r="O153" t="n">
         <v>30</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31392,9 +31179,6 @@
       <c r="O156" t="n">
         <v>12</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31785,9 +31569,6 @@
       <c r="O158" t="n">
         <v>23</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32405,9 +32186,6 @@
       <c r="O161" t="n">
         <v>5</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32798,9 +32576,6 @@
       <c r="O163" t="n">
         <v>19</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33418,9 +33193,6 @@
       <c r="O166" t="n">
         <v>3</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33811,9 +33583,6 @@
       <c r="O168" t="n">
         <v>19</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34431,9 +34200,6 @@
       <c r="O171" t="n">
         <v>9</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34824,9 +34590,6 @@
       <c r="O173" t="n">
         <v>9</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35444,9 +35207,6 @@
       <c r="O176" t="n">
         <v>8</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35837,9 +35597,6 @@
       <c r="O178" t="n">
         <v>13</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36457,9 +36214,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="S181" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36850,9 +36604,6 @@
       <c r="O183" t="n">
         <v>21</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="S183" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37470,9 +37221,6 @@
       <c r="O186" t="n">
         <v>6</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37863,9 +37611,6 @@
       <c r="O188" t="n">
         <v>48</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38483,9 +38228,6 @@
       <c r="O191" t="n">
         <v>11</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38876,9 +38618,6 @@
       <c r="O193" t="n">
         <v>62</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39496,9 +39235,6 @@
       <c r="O196" t="n">
         <v>21</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39889,9 +39625,6 @@
       <c r="O198" t="n">
         <v>86</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40509,9 +40242,6 @@
       <c r="O201" t="n">
         <v>24</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40902,9 +40632,6 @@
       <c r="O203" t="n">
         <v>72</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41522,9 +41249,6 @@
       <c r="O206" t="n">
         <v>44</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41915,9 +41639,6 @@
       <c r="O208" t="n">
         <v>55</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42535,9 +42256,6 @@
       <c r="O211" t="n">
         <v>20</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42928,9 +42646,6 @@
       <c r="O213" t="n">
         <v>25</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43548,9 +43263,6 @@
       <c r="O216" t="n">
         <v>17</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43941,9 +43653,6 @@
       <c r="O218" t="n">
         <v>23</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44561,9 +44270,6 @@
       <c r="O221" t="n">
         <v>24</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44954,9 +44660,6 @@
       <c r="O223" t="n">
         <v>22</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45574,9 +45277,6 @@
       <c r="O226" t="n">
         <v>9</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45967,9 +45667,6 @@
       <c r="O228" t="n">
         <v>24</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46587,9 +46284,6 @@
       <c r="O231" t="n">
         <v>7</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46980,9 +46674,6 @@
       <c r="O233" t="n">
         <v>18</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47600,9 +47291,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47993,9 +47681,6 @@
       <c r="O238" t="n">
         <v>21</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48613,9 +48298,6 @@
       <c r="O241" t="n">
         <v>7</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49006,9 +48688,6 @@
       <c r="O243" t="n">
         <v>17</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49626,9 +49305,6 @@
       <c r="O246" t="n">
         <v>7</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50019,9 +49695,6 @@
       <c r="O248" t="n">
         <v>29</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50639,9 +50312,6 @@
       <c r="O251" t="n">
         <v>4</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51032,9 +50702,6 @@
       <c r="O253" t="n">
         <v>37</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="S253" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51652,9 +51319,6 @@
       <c r="O256" t="n">
         <v>15</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52045,9 +51709,6 @@
       <c r="O258" t="n">
         <v>59</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52665,9 +52326,6 @@
       <c r="O261" t="n">
         <v>32</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53058,9 +52716,6 @@
       <c r="O263" t="n">
         <v>56</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53678,9 +53333,6 @@
       <c r="O266" t="n">
         <v>24</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54071,9 +53723,6 @@
       <c r="O268" t="n">
         <v>55</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54691,9 +54340,6 @@
       <c r="O271" t="n">
         <v>16</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55084,9 +54730,6 @@
       <c r="O273" t="n">
         <v>43</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="S273" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55703,9 +55346,6 @@
       </c>
       <c r="O276" t="n">
         <v>11</v>
-      </c>
-      <c r="Q276" t="n">
-        <v>0</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>

--- a/diseases/d109/1995-1999.xlsx
+++ b/diseases/d109/1995-1999.xlsx
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1185,17 +1185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1411,7 +1416,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1419,17 +1424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1957,7 +1967,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2191,7 +2206,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2737,7 +2757,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2971,7 +2996,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3517,7 +3547,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3751,7 +3786,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -4297,7 +4337,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4531,7 +4576,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -5077,7 +5127,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5135,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5311,7 +5366,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5374,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5857,7 +5917,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5865,17 +5925,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6091,7 +6156,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6099,17 +6164,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6637,7 +6707,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6715,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6871,7 +6946,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +6954,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -7417,7 +7497,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7505,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7651,7 +7736,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7744,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -8197,7 +8287,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8295,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8431,7 +8526,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8534,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8977,7 +9077,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9085,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9211,7 +9316,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9324,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9757,7 +9867,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9875,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9991,7 +10106,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,17 +10114,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10537,7 +10657,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10545,17 +10665,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10771,7 +10896,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10779,17 +10904,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -11317,7 +11447,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11325,17 +11455,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11551,7 +11686,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -11559,17 +11694,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -12097,7 +12237,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12105,17 +12245,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12331,7 +12476,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12339,17 +12484,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12877,7 +13027,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12885,17 +13035,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -13111,7 +13266,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13119,17 +13274,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13657,7 +13817,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13665,17 +13825,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13891,7 +14056,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13899,17 +14064,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14437,7 +14607,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14445,17 +14615,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14671,7 +14846,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14679,17 +14854,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -15217,7 +15397,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -15225,17 +15405,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -15451,7 +15636,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -15459,17 +15644,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -15997,7 +16187,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -16005,17 +16195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -16231,7 +16426,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -16239,17 +16434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -16777,7 +16977,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -16785,17 +16985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -17011,7 +17216,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -17019,17 +17224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -17557,7 +17767,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -17565,17 +17775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -17791,7 +18006,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -17799,17 +18014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -18337,7 +18557,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -18345,17 +18565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS92" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -18571,7 +18796,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -18579,17 +18804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS93" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -19117,7 +19347,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -19125,17 +19355,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -19351,7 +19586,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -19359,17 +19594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -19967,26 +20207,30 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -20124,7 +20368,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -20132,17 +20376,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -20358,7 +20607,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -20366,17 +20615,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -20974,26 +21228,30 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -21131,7 +21389,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -21139,17 +21397,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -21365,7 +21628,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -21373,17 +21636,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -21981,26 +22249,30 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -22138,7 +22410,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -22146,17 +22418,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -22372,7 +22649,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
@@ -22380,17 +22657,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS112" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -22988,26 +23270,30 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -23145,7 +23431,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -23153,17 +23439,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -23379,7 +23670,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -23387,17 +23678,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS117" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -23995,26 +24291,30 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -24152,7 +24452,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -24160,17 +24460,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -24386,7 +24691,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -24394,17 +24699,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS122" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -25002,26 +25312,30 @@
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -25159,7 +25473,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
@@ -25167,17 +25481,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS126" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -25393,7 +25712,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
@@ -25401,17 +25720,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS127" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -26009,26 +26333,30 @@
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -26166,7 +26494,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
@@ -26174,17 +26502,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS131" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -26400,7 +26733,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -26408,17 +26741,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS132" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -27016,26 +27354,30 @@
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -27173,7 +27515,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -27181,17 +27523,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -27407,7 +27754,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -27415,17 +27762,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -28023,26 +28375,30 @@
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -28180,7 +28536,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -28188,17 +28544,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -28414,7 +28775,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -28422,17 +28783,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS142" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -29030,26 +29396,30 @@
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -29187,7 +29557,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
@@ -29195,17 +29565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS146" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -29421,7 +29796,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
@@ -29429,17 +29804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS147" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -30037,26 +30417,30 @@
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -30194,7 +30578,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -30202,17 +30586,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS151" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -30428,7 +30817,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -30436,17 +30825,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS152" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -31044,26 +31438,30 @@
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -31201,7 +31599,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -31209,17 +31607,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -31435,7 +31838,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -31443,17 +31846,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS157" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -32051,26 +32459,30 @@
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -32208,7 +32620,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -32216,17 +32628,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS161" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -32442,7 +32859,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
@@ -32450,17 +32867,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS162" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -33058,26 +33480,30 @@
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -33215,7 +33641,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
@@ -33223,17 +33649,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS166" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -33449,7 +33880,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
@@ -33457,17 +33888,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS167" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -34065,26 +34501,30 @@
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -34222,7 +34662,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -34230,17 +34670,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS171" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -34456,7 +34901,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -34464,17 +34909,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -35072,26 +35522,30 @@
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -35229,7 +35683,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -35237,17 +35691,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -35463,7 +35922,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -35471,17 +35930,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS177" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -36079,26 +36543,30 @@
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -36236,7 +36704,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -36244,17 +36712,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS181" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -36470,7 +36943,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
@@ -36478,17 +36951,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS182" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -37086,26 +37564,30 @@
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -37243,7 +37725,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
@@ -37251,17 +37733,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS186" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -37477,7 +37964,7 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
@@ -37485,17 +37972,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS187" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -38093,26 +38585,30 @@
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -38250,7 +38746,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -38258,17 +38754,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS191" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -38484,7 +38985,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
@@ -38492,17 +38993,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS192" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
@@ -39100,26 +39606,30 @@
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -39257,7 +39767,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -39265,17 +39775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -39491,7 +40006,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -39499,17 +40014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS197" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -40107,26 +40627,30 @@
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -40264,7 +40788,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -40272,17 +40796,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -40498,7 +41027,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -40506,17 +41035,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS202" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -41114,26 +41648,30 @@
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -41271,7 +41809,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
@@ -41279,17 +41817,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS206" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -41505,7 +42048,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -41513,17 +42056,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS207" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -42121,26 +42669,30 @@
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -42278,7 +42830,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
@@ -42286,17 +42838,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS211" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -42512,7 +43069,7 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
@@ -42520,17 +43077,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS212" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -43128,26 +43690,30 @@
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -43285,7 +43851,7 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
@@ -43293,17 +43859,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS216" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -43519,7 +44090,7 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
@@ -43527,17 +44098,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS217" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -44135,26 +44711,30 @@
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -44292,7 +44872,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
@@ -44300,17 +44880,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS221" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -44526,7 +45111,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
@@ -44534,17 +45119,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS222" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -45142,26 +45732,30 @@
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -45299,7 +45893,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -45307,17 +45901,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS226" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -45533,7 +46132,7 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
@@ -45541,17 +46140,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS227" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -46149,26 +46753,30 @@
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
@@ -46306,7 +46914,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
@@ -46314,17 +46922,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS231" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
@@ -46540,7 +47153,7 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
@@ -46548,17 +47161,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS232" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
@@ -47156,26 +47774,30 @@
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -47313,7 +47935,7 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
@@ -47321,17 +47943,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS236" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -47547,7 +48174,7 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
@@ -47555,17 +48182,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS237" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
@@ -48163,26 +48795,30 @@
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -48320,7 +48956,7 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
@@ -48328,17 +48964,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS241" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -48554,7 +49195,7 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
@@ -48562,17 +49203,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS242" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
@@ -49170,26 +49816,30 @@
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
@@ -49327,7 +49977,7 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
@@ -49335,17 +49985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS246" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
@@ -49561,7 +50216,7 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
@@ -49569,17 +50224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS247" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
@@ -50177,26 +50837,30 @@
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
@@ -50334,7 +50998,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -50342,17 +51006,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
@@ -50568,7 +51237,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -50576,17 +51245,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS252" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
@@ -51184,26 +51858,30 @@
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -51341,7 +52019,7 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
@@ -51349,17 +52027,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS256" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
@@ -51575,7 +52258,7 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
@@ -51583,17 +52266,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS257" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
@@ -52191,26 +52879,30 @@
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -52348,7 +53040,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
@@ -52356,17 +53048,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS261" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -52582,7 +53279,7 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ262" t="inlineStr">
@@ -52590,17 +53287,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS262" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
@@ -53198,26 +53900,30 @@
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -53355,7 +54061,7 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ266" t="inlineStr">
@@ -53363,17 +54069,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS266" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
@@ -53589,7 +54300,7 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ267" t="inlineStr">
@@ -53597,17 +54308,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS267" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
@@ -54205,26 +54921,30 @@
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ270" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -54362,7 +55082,7 @@
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ271" t="inlineStr">
@@ -54370,17 +55090,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS271" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
@@ -54596,7 +55321,7 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ272" t="inlineStr">
@@ -54604,17 +55329,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS272" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
@@ -55212,26 +55942,30 @@
       </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
@@ -55369,7 +56103,7 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ276" t="inlineStr">
@@ -55377,17 +56111,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS276" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
@@ -55603,7 +56342,7 @@
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ277" t="inlineStr">
@@ -55611,17 +56350,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS277" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
